--- a/Spawning database_2025-08.xlsx
+++ b/Spawning database_2025-08.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8290" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8290" uniqueCount="306">
   <si>
     <t>ID.obs</t>
   </si>
@@ -75,7 +75,7 @@
     <t>Natural reef</t>
   </si>
   <si>
-    <t>Acropora sp.(digitate yellow thin)</t>
+    <t>Acropora sp. (digitate yellow thin)</t>
   </si>
   <si>
     <t>Mature</t>
@@ -105,7 +105,7 @@
     <t>A. formosa</t>
   </si>
   <si>
-    <t>Acropora sp.(digitate yellow smooth)</t>
+    <t>Acropora sp. (digitate yellow smooth)</t>
   </si>
   <si>
     <t>A. Secale</t>
@@ -114,7 +114,7 @@
     <t>Immature</t>
   </si>
   <si>
-    <t>Acropora sp.(digitate whitetip smooth)</t>
+    <t>Acropora sp. (digitate whitetip smooth)</t>
   </si>
   <si>
     <t>check</t>
@@ -123,13 +123,13 @@
     <t>6,7</t>
   </si>
   <si>
-    <t>Acropora sp.(corymbose smooth bluetip)</t>
+    <t>Acropora sp. (corymbose smooth bluetip)</t>
   </si>
   <si>
     <t>A. valida</t>
   </si>
   <si>
-    <t>Acropora sp.(digitate purpletip)</t>
+    <t>Acropora sp. (digitate purpletip)</t>
   </si>
   <si>
     <t>9,10</t>
@@ -138,7 +138,7 @@
     <t>White strands/coils?</t>
   </si>
   <si>
-    <t>Acropora sp.(digitate yellow fat)</t>
+    <t>Acropora sp. (digitate yellow fat)</t>
   </si>
   <si>
     <t>A. digitifera</t>
@@ -153,13 +153,13 @@
     <t xml:space="preserve">A. formosa </t>
   </si>
   <si>
-    <t>Acropora sp.(corymbose yellow smooth)</t>
+    <t>Acropora sp. (corymbose yellow smooth)</t>
   </si>
   <si>
     <t>Omar</t>
   </si>
   <si>
-    <t>Acropora sp.(corymbose whitetip smooth)</t>
+    <t>Acropora sp. (corymbose whitetip smooth)</t>
   </si>
   <si>
     <t>Acropora humilis</t>
@@ -171,7 +171,7 @@
     <t>Netted</t>
   </si>
   <si>
-    <t>Acropora sp.(corymbose yellow thin)</t>
+    <t>Acropora sp. (corymbose yellow thin)</t>
   </si>
   <si>
     <t>Maybe a few immature</t>
@@ -216,7 +216,7 @@
     <t>NET20230113_Acys</t>
   </si>
   <si>
-    <t>Acropora sp.(corymbose purpletip)</t>
+    <t>Acropora sp. (corymbose purpletip)</t>
   </si>
   <si>
     <t>NET20230113_Acp</t>
@@ -243,16 +243,16 @@
     <t>4,5</t>
   </si>
   <si>
-    <t>Acropora sp.(digitifera yellow thin)</t>
+    <t>Acropora sp. (digitifera yellow thin)</t>
   </si>
   <si>
     <t>6,7,8,</t>
   </si>
   <si>
-    <t>Acropora sp.(digitate normal smooth)</t>
+    <t>Acropora sp. (digitate normal smooth)</t>
   </si>
   <si>
-    <t>Acropora sp.(corymbose normal smooth)</t>
+    <t>Acropora sp. (corymbose normal smooth)</t>
   </si>
   <si>
     <t>Almost mature</t>
@@ -318,7 +318,7 @@
     <t>White spots: only a couple: might have been tentacles instead</t>
   </si>
   <si>
-    <t>Acropora sp.(caespitose yellow thin)</t>
+    <t>Acropora sp. (caespitose yellow thin)</t>
   </si>
   <si>
     <t>White spots (can't be seen on pics)</t>
@@ -327,7 +327,7 @@
     <t>Looks like immature on pic</t>
   </si>
   <si>
-    <t>Acropora sp.(corymbose normal thin)</t>
+    <t>Acropora sp. (corymbose normal thin)</t>
   </si>
   <si>
     <t>Mwanaisha</t>
@@ -450,7 +450,7 @@
     <t>Tree 235</t>
   </si>
   <si>
-    <t>Acropora sp.(digitate)</t>
+    <t>Acropora sp. (digitate)</t>
   </si>
   <si>
     <t>White strands, some white other stuff</t>
@@ -642,7 +642,7 @@
     <t>Light pink</t>
   </si>
   <si>
-    <t>Acropora latistella</t>
+    <t>Acropora cf. latistella</t>
   </si>
   <si>
     <t>Acropora sp (table fluor green); Sietske: A. hyacinthus</t>
@@ -654,7 +654,7 @@
     <t>A. forskali</t>
   </si>
   <si>
-    <t>Acropora sp.(digitate yellow)</t>
+    <t>Acropora sp. (digitate yellow)</t>
   </si>
   <si>
     <t>Tree 052</t>
@@ -663,13 +663,13 @@
     <t>slimy</t>
   </si>
   <si>
-    <t>Acropora sp.(caespitose fine)</t>
+    <t>Acropora sp. (caespitose fine)</t>
   </si>
   <si>
-    <t>Acropora sp.(corymbose thin bulbous)</t>
+    <t>Acropora sp. (corymbose thin bulbous)</t>
   </si>
   <si>
-    <t>Acropora sp.(corymbose thin hydroid)</t>
+    <t>Acropora sp. (corymbose thin hydroid)</t>
   </si>
   <si>
     <t>A. appressa</t>
@@ -709,6 +709,9 @@
   </si>
   <si>
     <t>CMA</t>
+  </si>
+  <si>
+    <t>Acropora latistella</t>
   </si>
   <si>
     <t>Acropora natalensis</t>
@@ -31983,7 +31986,7 @@
         <v>3.0</v>
       </c>
       <c r="I715" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M715" s="1">
         <v>60.0</v>
@@ -32023,7 +32026,7 @@
         <v>3.9</v>
       </c>
       <c r="I716" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M716" s="1">
         <v>80.0</v>
@@ -32060,7 +32063,7 @@
         <v>4.1</v>
       </c>
       <c r="I717" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M717" s="1">
         <v>70.0</v>
@@ -32072,7 +32075,7 @@
         <v>55</v>
       </c>
       <c r="P717" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q717" s="16"/>
       <c r="R717" s="14" t="s">
@@ -32137,7 +32140,7 @@
         <v>2.2</v>
       </c>
       <c r="I719" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M719" s="1">
         <v>80.0</v>
@@ -32174,7 +32177,7 @@
         <v>1.8</v>
       </c>
       <c r="I720" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M720" s="1">
         <v>80.0</v>
@@ -32211,7 +32214,7 @@
         <v>1.1</v>
       </c>
       <c r="I721" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M721" s="1">
         <v>80.0</v>
@@ -32248,7 +32251,7 @@
         <v>1.3</v>
       </c>
       <c r="I722" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M722" s="1">
         <v>80.0</v>
@@ -32322,7 +32325,7 @@
         <v>1.2</v>
       </c>
       <c r="I724" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M724" s="1">
         <v>60.0</v>
@@ -32334,7 +32337,7 @@
         <v>55</v>
       </c>
       <c r="P724" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q724" s="16"/>
       <c r="R724" s="14" t="s">
@@ -32399,7 +32402,7 @@
         <v>1.8</v>
       </c>
       <c r="I726" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M726" s="1">
         <v>50.0</v>
@@ -32436,7 +32439,7 @@
         <v>2.8</v>
       </c>
       <c r="I727" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M727" s="1">
         <v>80.0</v>
@@ -32476,7 +32479,7 @@
         <v>3.4</v>
       </c>
       <c r="I728" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M728" s="1">
         <v>80.0</v>
@@ -32513,7 +32516,7 @@
         <v>3.5</v>
       </c>
       <c r="I729" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M729" s="1">
         <v>60.0</v>
@@ -32550,7 +32553,7 @@
         <v>2.4</v>
       </c>
       <c r="I730" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M730" s="1">
         <v>60.0</v>
@@ -32590,7 +32593,7 @@
         <v>2.5</v>
       </c>
       <c r="I731" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M731" s="1">
         <v>70.0</v>
@@ -32682,7 +32685,7 @@
         <v>55</v>
       </c>
       <c r="P733" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q733" s="16"/>
       <c r="R733" s="14" t="s">
@@ -32710,7 +32713,7 @@
         <v>2.7</v>
       </c>
       <c r="I734" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M734" s="1">
         <v>80.0</v>
@@ -32784,7 +32787,7 @@
         <v>3.4</v>
       </c>
       <c r="I736" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M736" s="1">
         <v>80.0</v>
@@ -32873,7 +32876,7 @@
         <v>55</v>
       </c>
       <c r="P738" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q738" s="16"/>
       <c r="R738" s="14" t="s">
@@ -32938,7 +32941,7 @@
         <v>2.3</v>
       </c>
       <c r="I740" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M740" s="1">
         <v>70.0</v>
@@ -33012,7 +33015,7 @@
         <v>1.7</v>
       </c>
       <c r="I742" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M742" s="1">
         <v>60.0</v>
@@ -33043,7 +33046,7 @@
         <v>3.0</v>
       </c>
       <c r="E743" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G743" s="1" t="s">
         <v>23</v>
@@ -33083,7 +33086,7 @@
         <v>3.0</v>
       </c>
       <c r="E744" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G744" s="1" t="s">
         <v>23</v>
@@ -33104,7 +33107,7 @@
         <v>55</v>
       </c>
       <c r="P744" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q744" s="16"/>
       <c r="R744" s="14" t="s">
@@ -33123,7 +33126,7 @@
         <v>3.0</v>
       </c>
       <c r="E745" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G745" s="1" t="s">
         <v>23</v>
@@ -33144,7 +33147,7 @@
         <v>55</v>
       </c>
       <c r="P745" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q745" s="16"/>
       <c r="R745" s="14" t="s">
@@ -33163,7 +33166,7 @@
         <v>3.0</v>
       </c>
       <c r="E746" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G746" s="1" t="s">
         <v>23</v>
@@ -33203,7 +33206,7 @@
         <v>3.0</v>
       </c>
       <c r="E747" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G747" s="1" t="s">
         <v>23</v>
@@ -33240,7 +33243,7 @@
         <v>3.0</v>
       </c>
       <c r="E748" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G748" s="1" t="s">
         <v>23</v>
@@ -33289,7 +33292,7 @@
         <v>2.6</v>
       </c>
       <c r="I749" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M749" s="1">
         <v>60.0</v>
@@ -33329,7 +33332,7 @@
         <v>2.1</v>
       </c>
       <c r="I750" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M750" s="1">
         <v>80.0</v>
@@ -33446,7 +33449,7 @@
         <v>1.8</v>
       </c>
       <c r="I753" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M753" s="1">
         <v>60.0</v>
@@ -33483,7 +33486,7 @@
         <v>2.6</v>
       </c>
       <c r="I754" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M754" s="1">
         <v>70.0</v>
@@ -33520,7 +33523,7 @@
         <v>2.4</v>
       </c>
       <c r="I755" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M755" s="1">
         <v>70.0</v>
@@ -33671,7 +33674,7 @@
         <v>3.1</v>
       </c>
       <c r="I759" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M759" s="1">
         <v>80.0</v>
@@ -33708,7 +33711,7 @@
         <v>3.2</v>
       </c>
       <c r="I760" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M760" s="1">
         <v>70.0</v>
@@ -33748,7 +33751,7 @@
         <v>3.8</v>
       </c>
       <c r="I761" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M761" s="1">
         <v>80.0</v>
@@ -33859,7 +33862,7 @@
         <v>3.1</v>
       </c>
       <c r="I764" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M764" s="1">
         <v>80.0</v>
@@ -33896,7 +33899,7 @@
         <v>3.0</v>
       </c>
       <c r="I765" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M765" s="1">
         <v>80.0</v>
@@ -33933,7 +33936,7 @@
         <v>2.8</v>
       </c>
       <c r="I766" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M766" s="1">
         <v>80.0</v>
@@ -33970,7 +33973,7 @@
         <v>2.6</v>
       </c>
       <c r="I767" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M767" s="1">
         <v>80.0</v>
@@ -33982,7 +33985,7 @@
         <v>55</v>
       </c>
       <c r="P767" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q767" s="16"/>
       <c r="R767" s="14" t="s">
@@ -34010,7 +34013,7 @@
         <v>1.8</v>
       </c>
       <c r="I768" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M768" s="1">
         <v>60.0</v>
@@ -34059,7 +34062,7 @@
         <v>55</v>
       </c>
       <c r="P769" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q769" s="16"/>
       <c r="R769" s="14" t="s">
@@ -34087,7 +34090,7 @@
         <v>2.3</v>
       </c>
       <c r="I770" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M770" s="1">
         <v>70.0</v>
@@ -34099,7 +34102,7 @@
         <v>55</v>
       </c>
       <c r="P770" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q770" s="16"/>
       <c r="R770" s="14" t="s">
@@ -34719,7 +34722,7 @@
         <v>7.1</v>
       </c>
       <c r="I787" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M787" s="1">
         <v>60.0</v>
@@ -34731,7 +34734,7 @@
         <v>55</v>
       </c>
       <c r="P787" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q787" s="16"/>
       <c r="R787" s="14" t="s">
@@ -34750,7 +34753,7 @@
         <v>16.0</v>
       </c>
       <c r="E788" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G788" s="1" t="s">
         <v>23</v>
@@ -34787,7 +34790,7 @@
         <v>16.0</v>
       </c>
       <c r="E789" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G789" s="1" t="s">
         <v>23</v>
@@ -34824,7 +34827,7 @@
         <v>16.0</v>
       </c>
       <c r="E790" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G790" s="1" t="s">
         <v>23</v>
@@ -34861,7 +34864,7 @@
         <v>16.0</v>
       </c>
       <c r="E791" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G791" s="1" t="s">
         <v>23</v>
@@ -34898,7 +34901,7 @@
         <v>16.0</v>
       </c>
       <c r="E792" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G792" s="1" t="s">
         <v>23</v>
@@ -34935,7 +34938,7 @@
         <v>16.0</v>
       </c>
       <c r="E793" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G793" s="1" t="s">
         <v>23</v>
@@ -34972,7 +34975,7 @@
         <v>16.0</v>
       </c>
       <c r="E794" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G794" s="1" t="s">
         <v>23</v>
@@ -35009,7 +35012,7 @@
         <v>16.0</v>
       </c>
       <c r="E795" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G795" s="1" t="s">
         <v>23</v>
@@ -35046,7 +35049,7 @@
         <v>16.0</v>
       </c>
       <c r="E796" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G796" s="1" t="s">
         <v>23</v>
@@ -35083,7 +35086,7 @@
         <v>16.0</v>
       </c>
       <c r="E797" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G797" s="1" t="s">
         <v>23</v>
@@ -35120,7 +35123,7 @@
         <v>16.0</v>
       </c>
       <c r="E798" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G798" s="1" t="s">
         <v>23</v>
@@ -35141,7 +35144,7 @@
         <v>55</v>
       </c>
       <c r="P798" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q798" s="16"/>
       <c r="R798" s="14" t="s">
@@ -35160,7 +35163,7 @@
         <v>16.0</v>
       </c>
       <c r="E799" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G799" s="1" t="s">
         <v>23</v>
@@ -35197,7 +35200,7 @@
         <v>16.0</v>
       </c>
       <c r="E800" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G800" s="1" t="s">
         <v>23</v>
@@ -35281,7 +35284,7 @@
         <v>2.7</v>
       </c>
       <c r="I802" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M802" s="1">
         <v>50.0</v>
@@ -35321,7 +35324,7 @@
         <v>2.7</v>
       </c>
       <c r="I803" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M803" s="1">
         <v>60.0</v>
@@ -35410,7 +35413,7 @@
         <v>55</v>
       </c>
       <c r="P805" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q805" s="16"/>
       <c r="R805" s="14" t="s">
@@ -35478,7 +35481,7 @@
         <v>1.9</v>
       </c>
       <c r="I807" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M807" s="1">
         <v>70.0</v>
@@ -35527,7 +35530,7 @@
         <v>55</v>
       </c>
       <c r="P808" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q808" s="16"/>
       <c r="R808" s="14" t="s">
@@ -35555,7 +35558,7 @@
         <v>1.9</v>
       </c>
       <c r="I809" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M809" s="1">
         <v>70.0</v>
@@ -35592,7 +35595,7 @@
         <v>1.7</v>
       </c>
       <c r="I810" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M810" s="1">
         <v>70.0</v>
@@ -35706,7 +35709,7 @@
         <v>2.2</v>
       </c>
       <c r="I813" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M813" s="1">
         <v>80.0</v>
@@ -35746,7 +35749,7 @@
         <v>2.4</v>
       </c>
       <c r="I814" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M814" s="1">
         <v>80.0</v>
@@ -35783,7 +35786,7 @@
         <v>1.7</v>
       </c>
       <c r="I815" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M815" s="1">
         <v>50.0</v>
@@ -35823,7 +35826,7 @@
         <v>1.9</v>
       </c>
       <c r="I816" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M816" s="1">
         <v>60.0</v>
@@ -35937,7 +35940,7 @@
         <v>2.3</v>
       </c>
       <c r="I819" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M819" s="1">
         <v>80.0</v>
@@ -35949,7 +35952,7 @@
         <v>55</v>
       </c>
       <c r="P819" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q819" s="16"/>
       <c r="R819" s="14" t="s">
@@ -35977,7 +35980,7 @@
         <v>2.6</v>
       </c>
       <c r="I820" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M820" s="1">
         <v>70.0</v>
@@ -36014,7 +36017,7 @@
         <v>3.1</v>
       </c>
       <c r="I821" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M821" s="1">
         <v>70.0</v>
@@ -36026,7 +36029,7 @@
         <v>55</v>
       </c>
       <c r="P821" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q821" s="16"/>
       <c r="R821" s="14" t="s">
@@ -36091,7 +36094,7 @@
         <v>3.8</v>
       </c>
       <c r="I823" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M823" s="1">
         <v>80.0</v>
@@ -36128,7 +36131,7 @@
         <v>3.8</v>
       </c>
       <c r="I824" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M824" s="1">
         <v>70.0</v>
@@ -36538,7 +36541,7 @@
         <v>3.0</v>
       </c>
       <c r="I835" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M835" s="1">
         <v>30.0</v>
@@ -36550,7 +36553,7 @@
         <v>105</v>
       </c>
       <c r="P835" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q835" s="16"/>
       <c r="R835" s="14" t="s">
@@ -36578,7 +36581,7 @@
         <v>3.6</v>
       </c>
       <c r="I836" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M836" s="1">
         <v>35.0</v>
@@ -36615,7 +36618,7 @@
         <v>3.4</v>
       </c>
       <c r="I837" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M837" s="1">
         <v>40.0</v>
@@ -36652,7 +36655,7 @@
         <v>2.9</v>
       </c>
       <c r="I838" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M838" s="1">
         <v>40.0</v>
@@ -36689,7 +36692,7 @@
         <v>3.0</v>
       </c>
       <c r="I839" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M839" s="1">
         <v>30.0</v>
@@ -36726,7 +36729,7 @@
         <v>3.3</v>
       </c>
       <c r="I840" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M840" s="1">
         <v>15.0</v>
@@ -36738,7 +36741,7 @@
         <v>105</v>
       </c>
       <c r="P840" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q840" s="16"/>
       <c r="R840" s="14" t="s">
@@ -36778,7 +36781,7 @@
         <v>105</v>
       </c>
       <c r="P841" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q841" s="16"/>
       <c r="R841" s="14" t="s">
@@ -36883,7 +36886,7 @@
         <v>2.9</v>
       </c>
       <c r="I844" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M844" s="1">
         <v>15.0</v>
@@ -36923,7 +36926,7 @@
         <v>2.0</v>
       </c>
       <c r="I845" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M845" s="1">
         <v>35.0</v>
@@ -36935,7 +36938,7 @@
         <v>105</v>
       </c>
       <c r="P845" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q845" s="16"/>
       <c r="R845" s="14" t="s">
@@ -36963,7 +36966,7 @@
         <v>3.8</v>
       </c>
       <c r="I846" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M846" s="1">
         <v>30.0</v>
@@ -37000,7 +37003,7 @@
         <v>3.3</v>
       </c>
       <c r="I847" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M847" s="1">
         <v>20.0</v>
@@ -37037,7 +37040,7 @@
         <v>3.2</v>
       </c>
       <c r="I848" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M848" s="1">
         <v>70.0</v>
@@ -37074,7 +37077,7 @@
         <v>2.9</v>
       </c>
       <c r="I849" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M849" s="1">
         <v>20.0</v>
@@ -37114,7 +37117,7 @@
         <v>3.7</v>
       </c>
       <c r="I850" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M850" s="1">
         <v>100.0</v>
@@ -37151,7 +37154,7 @@
         <v>2.6</v>
       </c>
       <c r="I851" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M851" s="1">
         <v>30.0</v>
@@ -37163,7 +37166,7 @@
         <v>22</v>
       </c>
       <c r="P851" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q851" s="16"/>
       <c r="R851" s="14" t="s">
@@ -37191,7 +37194,7 @@
         <v>3.2</v>
       </c>
       <c r="I852" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M852" s="1">
         <v>70.0</v>
@@ -37265,7 +37268,7 @@
         <v>3.8</v>
       </c>
       <c r="I854" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M854" s="1">
         <v>50.0</v>
@@ -37305,7 +37308,7 @@
         <v>3.0</v>
       </c>
       <c r="I855" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M855" s="1">
         <v>60.0</v>
@@ -37416,7 +37419,7 @@
         <v>2.9</v>
       </c>
       <c r="I858" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M858" s="1">
         <v>60.0</v>
@@ -37490,7 +37493,7 @@
         <v>3.3</v>
       </c>
       <c r="I860" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M860" s="1">
         <v>40.0</v>
@@ -37601,7 +37604,7 @@
         <v>3.0</v>
       </c>
       <c r="I863" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M863" s="1">
         <v>60.0</v>
@@ -37638,7 +37641,7 @@
         <v>2.9</v>
       </c>
       <c r="I864" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M864" s="1">
         <v>30.0</v>
@@ -37650,7 +37653,7 @@
         <v>22</v>
       </c>
       <c r="P864" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q864" s="16"/>
       <c r="R864" s="14" t="s">
@@ -37669,7 +37672,7 @@
         <v>20.0</v>
       </c>
       <c r="E865" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G865" s="1" t="s">
         <v>23</v>
@@ -37706,7 +37709,7 @@
         <v>20.0</v>
       </c>
       <c r="E866" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G866" s="1" t="s">
         <v>23</v>
@@ -37743,7 +37746,7 @@
         <v>20.0</v>
       </c>
       <c r="E867" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G867" s="1" t="s">
         <v>125</v>
@@ -37780,7 +37783,7 @@
         <v>20.0</v>
       </c>
       <c r="E868" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G868" s="1" t="s">
         <v>125</v>
@@ -37826,7 +37829,7 @@
         <v>3.4</v>
       </c>
       <c r="I869" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M869" s="1">
         <v>40.0</v>
@@ -37863,7 +37866,7 @@
         <v>2.4</v>
       </c>
       <c r="I870" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M870" s="1">
         <v>55.0</v>
@@ -37900,7 +37903,7 @@
         <v>2.4</v>
       </c>
       <c r="I871" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M871" s="1">
         <v>80.0</v>
@@ -38011,7 +38014,7 @@
         <v>2.5</v>
       </c>
       <c r="I874" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M874" s="1">
         <v>25.0</v>
@@ -38060,7 +38063,7 @@
         <v>22</v>
       </c>
       <c r="P875" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q875" s="16"/>
       <c r="R875" s="14" t="s">
@@ -38100,7 +38103,7 @@
         <v>22</v>
       </c>
       <c r="P876" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q876" s="16"/>
       <c r="R876" s="14" t="s">
@@ -38128,7 +38131,7 @@
         <v>3.5</v>
       </c>
       <c r="I877" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M877" s="1">
         <v>35.0</v>
@@ -38165,7 +38168,7 @@
         <v>3.8</v>
       </c>
       <c r="I878" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M878" s="1">
         <v>90.0</v>
@@ -38276,7 +38279,7 @@
         <v>2.4</v>
       </c>
       <c r="I881" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M881" s="1">
         <v>60.0</v>
@@ -38313,7 +38316,7 @@
         <v>2.9</v>
       </c>
       <c r="I882" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M882" s="1">
         <v>55.0</v>
@@ -38325,7 +38328,7 @@
         <v>22</v>
       </c>
       <c r="P882" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q882" s="16"/>
       <c r="R882" s="14" t="s">
@@ -38464,7 +38467,7 @@
         <v>2.9</v>
       </c>
       <c r="I886" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M886" s="1">
         <v>80.0</v>
@@ -38501,7 +38504,7 @@
         <v>2.3</v>
       </c>
       <c r="I887" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M887" s="1">
         <v>35.0</v>
@@ -38575,7 +38578,7 @@
         <v>2.6</v>
       </c>
       <c r="I889" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M889" s="1">
         <v>35.0</v>
@@ -38612,7 +38615,7 @@
         <v>2.9</v>
       </c>
       <c r="I890" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M890" s="1">
         <v>40.0</v>
@@ -38686,7 +38689,7 @@
         <v>2.3</v>
       </c>
       <c r="I892" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M892" s="1">
         <v>25.0</v>
@@ -38726,7 +38729,7 @@
         <v>2.9</v>
       </c>
       <c r="I893" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M893" s="1">
         <v>55.0</v>
@@ -38763,7 +38766,7 @@
         <v>2.9</v>
       </c>
       <c r="I894" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M894" s="1">
         <v>25.0</v>
@@ -38837,7 +38840,7 @@
         <v>3.3</v>
       </c>
       <c r="I896" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M896" s="1">
         <v>55.0</v>
@@ -38849,7 +38852,7 @@
         <v>105</v>
       </c>
       <c r="P896" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q896" s="16"/>
       <c r="R896" s="14" t="s">
@@ -38877,7 +38880,7 @@
         <v>2.6</v>
       </c>
       <c r="I897" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M897" s="1">
         <v>40.0</v>
@@ -38914,7 +38917,7 @@
         <v>2.0</v>
       </c>
       <c r="I898" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M898" s="1">
         <v>25.0</v>
@@ -39025,7 +39028,7 @@
         <v>2.4</v>
       </c>
       <c r="I901" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M901" s="1">
         <v>80.0</v>
@@ -39062,7 +39065,7 @@
         <v>1.8</v>
       </c>
       <c r="I902" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M902" s="1">
         <v>45.0</v>
@@ -39210,7 +39213,7 @@
         <v>2.0</v>
       </c>
       <c r="I906" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M906" s="1">
         <v>70.0</v>
@@ -39250,7 +39253,7 @@
         <v>1.8</v>
       </c>
       <c r="I907" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M907" s="1">
         <v>80.0</v>
@@ -39441,7 +39444,7 @@
         <v>2.3</v>
       </c>
       <c r="I912" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M912" s="1">
         <v>80.0</v>
@@ -39478,7 +39481,7 @@
         <v>2.4</v>
       </c>
       <c r="I913" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M913" s="1">
         <v>70.0</v>
@@ -39518,7 +39521,7 @@
         <v>2.5</v>
       </c>
       <c r="I914" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M914" s="1">
         <v>70.0</v>
@@ -39592,7 +39595,7 @@
         <v>2.3</v>
       </c>
       <c r="I916" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M916" s="1">
         <v>80.0</v>
@@ -39604,7 +39607,7 @@
         <v>55</v>
       </c>
       <c r="P916" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q916" s="16"/>
       <c r="R916" s="14" t="s">
@@ -39632,7 +39635,7 @@
         <v>2.1</v>
       </c>
       <c r="I917" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M917" s="1">
         <v>70.0</v>
@@ -39669,7 +39672,7 @@
         <v>2.3</v>
       </c>
       <c r="I918" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M918" s="1">
         <v>30.0</v>
@@ -39709,7 +39712,7 @@
         <v>2.5</v>
       </c>
       <c r="I919" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M919" s="1">
         <v>70.0</v>
@@ -39749,7 +39752,7 @@
         <v>2.5</v>
       </c>
       <c r="I920" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M920" s="1">
         <v>60.0</v>
@@ -39786,7 +39789,7 @@
         <v>3.1</v>
       </c>
       <c r="I921" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M921" s="1">
         <v>55.0</v>
@@ -39823,7 +39826,7 @@
         <v>3.5</v>
       </c>
       <c r="I922" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M922" s="1">
         <v>80.0</v>
@@ -39863,7 +39866,7 @@
         <v>3.8</v>
       </c>
       <c r="I923" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M923" s="1">
         <v>70.0</v>
@@ -39900,7 +39903,7 @@
         <v>3.2</v>
       </c>
       <c r="I924" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M924" s="1">
         <v>70.0</v>
@@ -39974,7 +39977,7 @@
         <v>3.3</v>
       </c>
       <c r="I926" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M926" s="1">
         <v>20.0</v>
@@ -40048,7 +40051,7 @@
         <v>3.5</v>
       </c>
       <c r="I928" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M928" s="1">
         <v>70.0</v>
@@ -40085,7 +40088,7 @@
         <v>3.5</v>
       </c>
       <c r="I929" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M929" s="1">
         <v>60.0</v>
@@ -40122,7 +40125,7 @@
         <v>3.2</v>
       </c>
       <c r="I930" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M930" s="1">
         <v>50.0</v>
@@ -40134,7 +40137,7 @@
         <v>55</v>
       </c>
       <c r="P930" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q930" s="16"/>
       <c r="R930" s="14" t="s">
@@ -40199,7 +40202,7 @@
         <v>2.5</v>
       </c>
       <c r="I932" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M932" s="1">
         <v>80.0</v>
@@ -40236,7 +40239,7 @@
         <v>4.2</v>
       </c>
       <c r="I933" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M933" s="1">
         <v>80.0</v>
@@ -40273,7 +40276,7 @@
         <v>4.3</v>
       </c>
       <c r="I934" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M934" s="1">
         <v>70.0</v>
@@ -40285,7 +40288,7 @@
         <v>55</v>
       </c>
       <c r="P934" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q934" s="16"/>
       <c r="R934" s="14" t="s">
@@ -40325,7 +40328,7 @@
         <v>55</v>
       </c>
       <c r="P935" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q935" s="16"/>
       <c r="R935" s="14" t="s">
@@ -40353,7 +40356,7 @@
         <v>4.3</v>
       </c>
       <c r="I936" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M936" s="1">
         <v>70.0</v>
@@ -40390,7 +40393,7 @@
         <v>4.5</v>
       </c>
       <c r="I937" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M937" s="1">
         <v>40.0</v>
@@ -40430,7 +40433,7 @@
         <v>3.7</v>
       </c>
       <c r="I938" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M938" s="1">
         <v>70.0</v>
@@ -40738,7 +40741,7 @@
         <v>55</v>
       </c>
       <c r="P946" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q946" s="16"/>
       <c r="R946" s="14" t="s">
@@ -40988,7 +40991,7 @@
         <v>3.5</v>
       </c>
       <c r="I953" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M953" s="1">
         <v>40.0</v>
@@ -41025,7 +41028,7 @@
         <v>3.6</v>
       </c>
       <c r="I954" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M954" s="1">
         <v>35.0</v>
@@ -41062,7 +41065,7 @@
         <v>3.5</v>
       </c>
       <c r="I955" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M955" s="1">
         <v>30.0</v>
@@ -41099,7 +41102,7 @@
         <v>3.3</v>
       </c>
       <c r="I956" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M956" s="1">
         <v>25.0</v>
@@ -41139,7 +41142,7 @@
         <v>3.8</v>
       </c>
       <c r="I957" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M957" s="1">
         <v>40.0</v>
@@ -41216,7 +41219,7 @@
         <v>3.6</v>
       </c>
       <c r="I959" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M959" s="1">
         <v>20.0</v>
@@ -41253,7 +41256,7 @@
         <v>4.6</v>
       </c>
       <c r="I960" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M960" s="1">
         <v>20.0</v>
@@ -41265,7 +41268,7 @@
         <v>105</v>
       </c>
       <c r="P960" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q960" s="16"/>
       <c r="R960" s="14" t="s">
@@ -41293,7 +41296,7 @@
         <v>4.2</v>
       </c>
       <c r="I961" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M961" s="1">
         <v>30.0</v>
@@ -41330,7 +41333,7 @@
         <v>3.4</v>
       </c>
       <c r="I962" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M962" s="1">
         <v>40.0</v>
@@ -41367,7 +41370,7 @@
         <v>3.8</v>
       </c>
       <c r="I963" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M963" s="1">
         <v>35.0</v>
@@ -41404,7 +41407,7 @@
         <v>3.7</v>
       </c>
       <c r="I964" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M964" s="1">
         <v>60.0</v>
@@ -41416,7 +41419,7 @@
         <v>105</v>
       </c>
       <c r="P964" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q964" s="16"/>
       <c r="R964" s="14" t="s">
@@ -41444,7 +41447,7 @@
         <v>3.3</v>
       </c>
       <c r="I965" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M965" s="1">
         <v>45.0</v>
@@ -41481,7 +41484,7 @@
         <v>3.3</v>
       </c>
       <c r="I966" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M966" s="1">
         <v>40.0</v>
@@ -41518,7 +41521,7 @@
         <v>3.7</v>
       </c>
       <c r="I967" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M967" s="1">
         <v>20.0</v>
@@ -41555,7 +41558,7 @@
         <v>2.8</v>
       </c>
       <c r="I968" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M968" s="1">
         <v>15.0</v>
@@ -41592,7 +41595,7 @@
         <v>3.1</v>
       </c>
       <c r="I969" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M969" s="1">
         <v>26.0</v>
@@ -41604,7 +41607,7 @@
         <v>105</v>
       </c>
       <c r="P969" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q969" s="16"/>
       <c r="R969" s="14" t="s">
@@ -41669,7 +41672,7 @@
         <v>4.1</v>
       </c>
       <c r="I971" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M971" s="1">
         <v>37.0</v>
@@ -41709,7 +41712,7 @@
         <v>3.4</v>
       </c>
       <c r="I972" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M972" s="1">
         <v>35.0</v>
@@ -41746,7 +41749,7 @@
         <v>3.6</v>
       </c>
       <c r="I973" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M973" s="1">
         <v>40.0</v>
@@ -41795,7 +41798,7 @@
         <v>105</v>
       </c>
       <c r="P974" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q974" s="16"/>
       <c r="R974" s="14" t="s">
@@ -41823,7 +41826,7 @@
         <v>5.2</v>
       </c>
       <c r="I975" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M975" s="1">
         <v>35.0</v>
@@ -41909,7 +41912,7 @@
         <v>55</v>
       </c>
       <c r="P977" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q977" s="16"/>
       <c r="R977" s="14" t="s">
@@ -41974,7 +41977,7 @@
         <v>3.9</v>
       </c>
       <c r="I979" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M979" s="1">
         <v>70.0</v>
@@ -42014,7 +42017,7 @@
         <v>4.5</v>
       </c>
       <c r="I980" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M980" s="1">
         <v>70.0</v>
@@ -42051,7 +42054,7 @@
         <v>3.7</v>
       </c>
       <c r="I981" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M981" s="1">
         <v>70.0</v>
@@ -42088,7 +42091,7 @@
         <v>3.8</v>
       </c>
       <c r="I982" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M982" s="1">
         <v>50.0</v>
@@ -42128,7 +42131,7 @@
         <v>3.9</v>
       </c>
       <c r="I983" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M983" s="1">
         <v>40.0</v>
@@ -42165,7 +42168,7 @@
         <v>3.8</v>
       </c>
       <c r="I984" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M984" s="1">
         <v>40.0</v>
@@ -42205,7 +42208,7 @@
         <v>3.6</v>
       </c>
       <c r="I985" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M985" s="1">
         <v>60.0</v>
@@ -42254,7 +42257,7 @@
         <v>55</v>
       </c>
       <c r="P986" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q986" s="16"/>
       <c r="R986" s="14" t="s">
@@ -42322,7 +42325,7 @@
         <v>4.3</v>
       </c>
       <c r="I988" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M988" s="1">
         <v>80.0</v>
@@ -42359,7 +42362,7 @@
         <v>3.8</v>
       </c>
       <c r="I989" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M989" s="1">
         <v>80.0</v>
@@ -42399,7 +42402,7 @@
         <v>3.2</v>
       </c>
       <c r="I990" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M990" s="1">
         <v>70.0</v>
@@ -42411,7 +42414,7 @@
         <v>55</v>
       </c>
       <c r="P990" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q990" s="16"/>
       <c r="R990" s="14" t="s">
@@ -42439,7 +42442,7 @@
         <v>4.2</v>
       </c>
       <c r="I991" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M991" s="1">
         <v>80.0</v>
@@ -42451,7 +42454,7 @@
         <v>55</v>
       </c>
       <c r="P991" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q991" s="16"/>
       <c r="R991" s="14" t="s">
@@ -42479,7 +42482,7 @@
         <v>4.4</v>
       </c>
       <c r="I992" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M992" s="1">
         <v>80.0</v>
@@ -42519,7 +42522,7 @@
         <v>4.5</v>
       </c>
       <c r="I993" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M993" s="1">
         <v>80.0</v>
@@ -42531,7 +42534,7 @@
         <v>55</v>
       </c>
       <c r="P993" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q993" s="16"/>
       <c r="R993" s="14" t="s">
@@ -42559,7 +42562,7 @@
         <v>4.5</v>
       </c>
       <c r="I994" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M994" s="1">
         <v>70.0</v>
@@ -42571,7 +42574,7 @@
         <v>55</v>
       </c>
       <c r="P994" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q994" s="16"/>
       <c r="R994" s="14" t="s">
@@ -42648,7 +42651,7 @@
         <v>55</v>
       </c>
       <c r="P996" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q996" s="16"/>
       <c r="R996" s="14" t="s">
@@ -42910,7 +42913,7 @@
         <v>55</v>
       </c>
       <c r="P1003" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q1003" s="16"/>
       <c r="R1003" s="14" t="s">
@@ -42950,7 +42953,7 @@
         <v>55</v>
       </c>
       <c r="P1004" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q1004" s="16"/>
       <c r="R1004" s="14" t="s">
@@ -43018,7 +43021,7 @@
         <v>5.5</v>
       </c>
       <c r="I1006" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M1006" s="1">
         <v>35.0</v>
@@ -43058,7 +43061,7 @@
         <v>4.5</v>
       </c>
       <c r="I1007" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1007" s="1">
         <v>25.0</v>
@@ -43110,7 +43113,7 @@
         <v>105</v>
       </c>
       <c r="P1008" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q1008" s="16"/>
       <c r="R1008" s="14" t="s">
@@ -43138,7 +43141,7 @@
         <v>4.1</v>
       </c>
       <c r="I1009" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1009" s="1">
         <v>20.0</v>
@@ -43178,7 +43181,7 @@
         <v>4.0</v>
       </c>
       <c r="I1010" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1010" s="1">
         <v>35.0</v>
@@ -43255,7 +43258,7 @@
         <v>3.5</v>
       </c>
       <c r="I1012" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1012" s="1">
         <v>35.0</v>
@@ -43267,7 +43270,7 @@
         <v>105</v>
       </c>
       <c r="P1012" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q1012" s="16"/>
       <c r="R1012" s="14" t="s">
@@ -43295,7 +43298,7 @@
         <v>3.4</v>
       </c>
       <c r="I1013" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1013" s="1">
         <v>30.0</v>
@@ -43335,7 +43338,7 @@
         <v>3.0</v>
       </c>
       <c r="I1014" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1014" s="1">
         <v>20.0</v>
@@ -43372,7 +43375,7 @@
         <v>3.2</v>
       </c>
       <c r="I1015" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M1015" s="1">
         <v>30.0</v>
@@ -43409,7 +43412,7 @@
         <v>3.5</v>
       </c>
       <c r="I1016" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1016" s="1">
         <v>30.0</v>
@@ -43483,7 +43486,7 @@
         <v>3.4</v>
       </c>
       <c r="I1018" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1018" s="1">
         <v>50.0</v>
@@ -43520,7 +43523,7 @@
         <v>3.6</v>
       </c>
       <c r="I1019" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1019" s="1">
         <v>20.0</v>
@@ -43770,7 +43773,7 @@
         <v>15.0</v>
       </c>
       <c r="E1026" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1026" s="1" t="s">
         <v>23</v>
@@ -43791,7 +43794,7 @@
         <v>55</v>
       </c>
       <c r="P1026" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q1026" s="16"/>
       <c r="R1026" s="14" t="s">
@@ -43810,7 +43813,7 @@
         <v>15.0</v>
       </c>
       <c r="E1027" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1027" s="1" t="s">
         <v>23</v>
@@ -43831,7 +43834,7 @@
         <v>55</v>
       </c>
       <c r="P1027" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q1027" s="16"/>
       <c r="R1027" s="14" t="s">
@@ -43850,7 +43853,7 @@
         <v>15.0</v>
       </c>
       <c r="E1028" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1028" s="1" t="s">
         <v>23</v>
@@ -43887,7 +43890,7 @@
         <v>15.0</v>
       </c>
       <c r="E1029" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1029" s="1" t="s">
         <v>23</v>
@@ -43924,7 +43927,7 @@
         <v>15.0</v>
       </c>
       <c r="E1030" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1030" s="1" t="s">
         <v>23</v>
@@ -43945,7 +43948,7 @@
         <v>55</v>
       </c>
       <c r="P1030" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q1030" s="16"/>
       <c r="R1030" s="14" t="s">
@@ -43964,7 +43967,7 @@
         <v>15.0</v>
       </c>
       <c r="E1031" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1031" s="1" t="s">
         <v>23</v>
@@ -44001,7 +44004,7 @@
         <v>15.0</v>
       </c>
       <c r="E1032" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1032" s="1" t="s">
         <v>19</v>
@@ -44010,7 +44013,7 @@
         <v>3.9</v>
       </c>
       <c r="I1032" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1032" s="1">
         <v>40.0</v>
@@ -44022,7 +44025,7 @@
         <v>55</v>
       </c>
       <c r="P1032" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q1032" s="16"/>
       <c r="R1032" s="14" t="s">
@@ -44041,7 +44044,7 @@
         <v>15.0</v>
       </c>
       <c r="E1033" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1033" s="1" t="s">
         <v>19</v>
@@ -44050,7 +44053,7 @@
         <v>5.6</v>
       </c>
       <c r="I1033" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1033" s="1">
         <v>70.0</v>
@@ -44062,7 +44065,7 @@
         <v>55</v>
       </c>
       <c r="P1033" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q1033" s="16"/>
       <c r="R1033" s="14" t="s">
@@ -44081,7 +44084,7 @@
         <v>15.0</v>
       </c>
       <c r="E1034" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1034" s="1" t="s">
         <v>23</v>
@@ -44102,7 +44105,7 @@
         <v>55</v>
       </c>
       <c r="P1034" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q1034" s="16"/>
       <c r="R1034" s="14" t="s">
@@ -44121,7 +44124,7 @@
         <v>15.0</v>
       </c>
       <c r="E1035" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1035" s="1" t="s">
         <v>23</v>
@@ -44130,7 +44133,7 @@
         <v>5.2</v>
       </c>
       <c r="I1035" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1035" s="1">
         <v>40.0</v>
@@ -44158,7 +44161,7 @@
         <v>15.0</v>
       </c>
       <c r="E1036" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1036" s="1" t="s">
         <v>23</v>
@@ -44167,7 +44170,7 @@
         <v>4.0</v>
       </c>
       <c r="I1036" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1036" s="1">
         <v>35.0</v>
@@ -44195,7 +44198,7 @@
         <v>15.0</v>
       </c>
       <c r="E1037" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1037" s="1" t="s">
         <v>23</v>
@@ -44204,7 +44207,7 @@
         <v>4.0</v>
       </c>
       <c r="I1037" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1037" s="1">
         <v>35.0</v>
@@ -44232,7 +44235,7 @@
         <v>15.0</v>
       </c>
       <c r="E1038" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1038" s="1" t="s">
         <v>23</v>
@@ -44253,7 +44256,7 @@
         <v>55</v>
       </c>
       <c r="P1038" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q1038" s="16"/>
       <c r="R1038" s="14" t="s">
@@ -44272,7 +44275,7 @@
         <v>15.0</v>
       </c>
       <c r="E1039" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1039" s="1" t="s">
         <v>23</v>
@@ -44293,7 +44296,7 @@
         <v>55</v>
       </c>
       <c r="P1039" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q1039" s="16"/>
       <c r="R1039" s="14" t="s">
@@ -44312,7 +44315,7 @@
         <v>15.0</v>
       </c>
       <c r="E1040" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1040" s="1" t="s">
         <v>23</v>
@@ -44333,7 +44336,7 @@
         <v>55</v>
       </c>
       <c r="P1040" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q1040" s="16"/>
       <c r="R1040" s="14" t="s">
@@ -44352,7 +44355,7 @@
         <v>15.0</v>
       </c>
       <c r="E1041" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G1041" s="1" t="s">
         <v>23</v>
@@ -44373,7 +44376,7 @@
         <v>55</v>
       </c>
       <c r="P1041" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q1041" s="16"/>
       <c r="R1041" s="14" t="s">
@@ -44413,7 +44416,7 @@
         <v>55</v>
       </c>
       <c r="P1042" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q1042" s="16"/>
       <c r="R1042" s="14" t="s">
@@ -44453,7 +44456,7 @@
         <v>55</v>
       </c>
       <c r="P1043" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q1043" s="16"/>
       <c r="R1043" s="14" t="s">
@@ -44530,7 +44533,7 @@
         <v>55</v>
       </c>
       <c r="P1045" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q1045" s="16"/>
       <c r="R1045" s="14" t="s">
@@ -44570,7 +44573,7 @@
         <v>55</v>
       </c>
       <c r="P1046" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q1046" s="16"/>
       <c r="R1046" s="14" t="s">
@@ -44635,7 +44638,7 @@
         <v>6.2</v>
       </c>
       <c r="I1048" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1048" s="1">
         <v>60.0</v>
@@ -44687,7 +44690,7 @@
         <v>55</v>
       </c>
       <c r="P1049" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q1049" s="16"/>
       <c r="R1049" s="14" t="s">
@@ -44915,7 +44918,7 @@
         <v>55</v>
       </c>
       <c r="P1055" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q1055" s="16"/>
       <c r="R1055" s="14" t="s">
@@ -44955,7 +44958,7 @@
         <v>55</v>
       </c>
       <c r="P1056" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q1056" s="16"/>
       <c r="R1056" s="14" t="s">
@@ -45020,7 +45023,7 @@
         <v>2.1</v>
       </c>
       <c r="I1058" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1058" s="1">
         <v>65.0</v>
@@ -45072,7 +45075,7 @@
         <v>55</v>
       </c>
       <c r="P1059" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q1059" s="16"/>
       <c r="R1059" s="14" t="s">
@@ -45100,7 +45103,7 @@
         <v>2.1</v>
       </c>
       <c r="I1060" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M1060" s="1">
         <v>80.0</v>
@@ -45137,7 +45140,7 @@
         <v>2.2</v>
       </c>
       <c r="I1061" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1061" s="1">
         <v>80.0</v>
@@ -45149,7 +45152,7 @@
         <v>55</v>
       </c>
       <c r="P1061" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q1061" s="16"/>
       <c r="R1061" s="14" t="s">
@@ -45177,7 +45180,7 @@
         <v>2.0</v>
       </c>
       <c r="I1062" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1062" s="1">
         <v>25.0</v>
@@ -45214,7 +45217,7 @@
         <v>2.0</v>
       </c>
       <c r="I1063" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1063" s="1">
         <v>60.0</v>
@@ -45251,7 +45254,7 @@
         <v>2.4</v>
       </c>
       <c r="I1064" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1064" s="1">
         <v>60.0</v>
@@ -45263,7 +45266,7 @@
         <v>55</v>
       </c>
       <c r="P1064" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q1064" s="16"/>
       <c r="R1064" s="14" t="s">
@@ -45291,7 +45294,7 @@
         <v>2.1</v>
       </c>
       <c r="I1065" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1065" s="1">
         <v>60.0</v>
@@ -45303,7 +45306,7 @@
         <v>55</v>
       </c>
       <c r="P1065" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q1065" s="16"/>
       <c r="R1065" s="14" t="s">
@@ -45331,7 +45334,7 @@
         <v>2.0</v>
       </c>
       <c r="I1066" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1066" s="1">
         <v>40.0</v>
@@ -45343,7 +45346,7 @@
         <v>55</v>
       </c>
       <c r="P1066" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q1066" s="16"/>
       <c r="R1066" s="14" t="s">
@@ -45371,7 +45374,7 @@
         <v>1.8</v>
       </c>
       <c r="I1067" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1067" s="1">
         <v>45.0</v>
@@ -45383,7 +45386,7 @@
         <v>55</v>
       </c>
       <c r="P1067" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q1067" s="16"/>
       <c r="R1067" s="14" t="s">
@@ -45411,7 +45414,7 @@
         <v>3.0</v>
       </c>
       <c r="I1068" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1068" s="1">
         <v>35.0</v>
@@ -45448,7 +45451,7 @@
         <v>3.0</v>
       </c>
       <c r="I1069" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1069" s="1">
         <v>60.0</v>
@@ -45522,7 +45525,7 @@
         <v>3.0</v>
       </c>
       <c r="I1071" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1071" s="1">
         <v>30.0</v>
@@ -45559,7 +45562,7 @@
         <v>3.0</v>
       </c>
       <c r="I1072" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1072" s="1">
         <v>30.0</v>
@@ -45571,7 +45574,7 @@
         <v>105</v>
       </c>
       <c r="P1072" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q1072" s="16"/>
       <c r="R1072" s="14" t="s">
@@ -45599,7 +45602,7 @@
         <v>2.0</v>
       </c>
       <c r="I1073" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1073" s="1">
         <v>45.0</v>
@@ -45636,7 +45639,7 @@
         <v>2.0</v>
       </c>
       <c r="I1074" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1074" s="1">
         <v>30.0</v>
@@ -45648,7 +45651,7 @@
         <v>105</v>
       </c>
       <c r="P1074" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q1074" s="16"/>
       <c r="R1074" s="14" t="s">
@@ -45676,7 +45679,7 @@
         <v>3.0</v>
       </c>
       <c r="I1075" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1075" s="1">
         <v>20.0</v>
@@ -45688,7 +45691,7 @@
         <v>105</v>
       </c>
       <c r="P1075" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q1075" s="16"/>
       <c r="R1075" s="14" t="s">
@@ -45716,7 +45719,7 @@
         <v>3.0</v>
       </c>
       <c r="I1076" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1076" s="1">
         <v>20.0</v>
@@ -45790,7 +45793,7 @@
         <v>3.8</v>
       </c>
       <c r="I1078" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1078" s="1">
         <v>40.0</v>
@@ -45827,7 +45830,7 @@
         <v>3.0</v>
       </c>
       <c r="I1079" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1079" s="1">
         <v>70.0</v>
@@ -45938,7 +45941,7 @@
         <v>2.6</v>
       </c>
       <c r="I1082" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1082" s="1">
         <v>100.0</v>
@@ -46012,7 +46015,7 @@
         <v>3.3</v>
       </c>
       <c r="I1084" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1084" s="1">
         <v>30.0</v>
@@ -46049,7 +46052,7 @@
         <v>3.3</v>
       </c>
       <c r="I1085" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1085" s="1">
         <v>30.0</v>
@@ -46098,7 +46101,7 @@
         <v>22</v>
       </c>
       <c r="P1086" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q1086" s="16"/>
       <c r="R1086" s="14" t="s">
@@ -46200,7 +46203,7 @@
         <v>2.7</v>
       </c>
       <c r="I1089" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1089" s="1">
         <v>40.0</v>
@@ -46237,7 +46240,7 @@
         <v>3.1</v>
       </c>
       <c r="I1090" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1090" s="1">
         <v>90.0</v>
@@ -46274,7 +46277,7 @@
         <v>3.2</v>
       </c>
       <c r="I1091" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1091" s="1">
         <v>90.0</v>
@@ -46286,7 +46289,7 @@
         <v>22</v>
       </c>
       <c r="P1091" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q1091" s="16"/>
       <c r="R1091" s="14" t="s">
@@ -46314,7 +46317,7 @@
         <v>2.3</v>
       </c>
       <c r="I1092" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1092" s="1">
         <v>60.0</v>
@@ -46326,7 +46329,7 @@
         <v>22</v>
       </c>
       <c r="P1092" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q1092" s="16"/>
       <c r="R1092" s="14" t="s">
@@ -46354,7 +46357,7 @@
         <v>2.3</v>
       </c>
       <c r="I1093" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M1093" s="1">
         <v>50.0</v>
@@ -46391,7 +46394,7 @@
         <v>2.3</v>
       </c>
       <c r="I1094" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1094" s="1">
         <v>25.0</v>
@@ -46687,7 +46690,7 @@
         <v>2.9</v>
       </c>
       <c r="I1102" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1102" s="1">
         <v>20.0</v>
@@ -46699,7 +46702,7 @@
         <v>22</v>
       </c>
       <c r="P1102" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q1102" s="16"/>
       <c r="R1102" s="14" t="s">
@@ -46776,7 +46779,7 @@
         <v>22</v>
       </c>
       <c r="P1104" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q1104" s="16"/>
       <c r="R1104" s="14" t="s">
@@ -46804,7 +46807,7 @@
         <v>2.2</v>
       </c>
       <c r="I1105" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M1105" s="1">
         <v>20.0</v>
@@ -46915,7 +46918,7 @@
         <v>3.0</v>
       </c>
       <c r="I1108" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M1108" s="1">
         <v>37.0</v>
@@ -46952,7 +46955,7 @@
         <v>2.0</v>
       </c>
       <c r="I1109" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M1109" s="1">
         <v>33.0</v>
@@ -47026,7 +47029,7 @@
         <v>3.1</v>
       </c>
       <c r="I1111" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1111" s="1">
         <v>50.0</v>
@@ -47063,7 +47066,7 @@
         <v>3.3</v>
       </c>
       <c r="I1112" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1112" s="1">
         <v>70.0</v>
@@ -47100,7 +47103,7 @@
         <v>2.4</v>
       </c>
       <c r="I1113" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1113" s="1">
         <v>40.0</v>
@@ -47177,7 +47180,7 @@
         <v>2.9</v>
       </c>
       <c r="I1115" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1115" s="1">
         <v>50.0</v>
@@ -47214,7 +47217,7 @@
         <v>4.2</v>
       </c>
       <c r="I1116" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1116" s="1">
         <v>35.0</v>
@@ -47254,7 +47257,7 @@
         <v>3.9</v>
       </c>
       <c r="I1117" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1117" s="1">
         <v>120.0</v>
@@ -47291,7 +47294,7 @@
         <v>3.2</v>
       </c>
       <c r="I1118" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M1118" s="1">
         <v>50.0</v>
@@ -47303,7 +47306,7 @@
         <v>22</v>
       </c>
       <c r="P1118" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q1118" s="16"/>
       <c r="R1118" s="14" t="s">
@@ -47408,7 +47411,7 @@
         <v>8.0</v>
       </c>
       <c r="I1121" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1121" s="1">
         <v>60.0</v>
@@ -47593,7 +47596,7 @@
         <v>4.0</v>
       </c>
       <c r="I1126" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1126" s="1">
         <v>35.0</v>
@@ -47704,7 +47707,7 @@
         <v>3.0</v>
       </c>
       <c r="I1129" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1129" s="1">
         <v>30.0</v>
@@ -47716,7 +47719,7 @@
         <v>105</v>
       </c>
       <c r="P1129" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q1129" s="16"/>
       <c r="R1129" s="14" t="s">
@@ -47744,7 +47747,7 @@
         <v>3.0</v>
       </c>
       <c r="I1130" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1130" s="1">
         <v>40.0</v>
@@ -47781,7 +47784,7 @@
         <v>3.0</v>
       </c>
       <c r="I1131" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1131" s="1">
         <v>25.0</v>
@@ -47855,7 +47858,7 @@
         <v>3.0</v>
       </c>
       <c r="I1133" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1133" s="1">
         <v>35.0</v>
@@ -47895,7 +47898,7 @@
         <v>2.0</v>
       </c>
       <c r="I1134" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1134" s="1">
         <v>17.0</v>
@@ -47907,7 +47910,7 @@
         <v>105</v>
       </c>
       <c r="P1134" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q1134" s="16"/>
       <c r="R1134" s="14" t="s">
@@ -47935,7 +47938,7 @@
         <v>2.0</v>
       </c>
       <c r="I1135" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1135" s="1">
         <v>17.0</v>
@@ -48021,7 +48024,7 @@
         <v>105</v>
       </c>
       <c r="P1137" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q1137" s="16"/>
       <c r="R1137" s="14" t="s">
@@ -48086,7 +48089,7 @@
         <v>2.0</v>
       </c>
       <c r="I1139" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M1139" s="1">
         <v>35.0</v>
@@ -48283,7 +48286,7 @@
         <v>105</v>
       </c>
       <c r="P1144" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q1144" s="16"/>
       <c r="R1144" s="14" t="s">
@@ -48348,7 +48351,7 @@
         <v>2.0</v>
       </c>
       <c r="I1146" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M1146" s="1">
         <v>40.0</v>
@@ -48385,7 +48388,7 @@
         <v>2.0</v>
       </c>
       <c r="I1147" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1147" s="1">
         <v>35.0</v>
@@ -48422,7 +48425,7 @@
         <v>2.0</v>
       </c>
       <c r="I1148" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M1148" s="1">
         <v>17.0</v>
@@ -48459,7 +48462,7 @@
         <v>2.0</v>
       </c>
       <c r="I1149" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M1149" s="1">
         <v>13.0</v>
@@ -48533,7 +48536,7 @@
         <v>4.5</v>
       </c>
       <c r="I1151" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1151" s="1">
         <v>60.0</v>
@@ -48545,7 +48548,7 @@
         <v>55</v>
       </c>
       <c r="P1151" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q1151" s="16"/>
       <c r="R1151" s="14" t="s">
@@ -48610,7 +48613,7 @@
         <v>2.9</v>
       </c>
       <c r="I1153" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M1153" s="1">
         <v>70.0</v>
@@ -48647,7 +48650,7 @@
         <v>2.0</v>
       </c>
       <c r="I1154" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M1154" s="1">
         <v>70.0</v>
@@ -48721,7 +48724,7 @@
         <v>1.8</v>
       </c>
       <c r="I1156" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1156" s="1">
         <v>30.0</v>
@@ -48733,7 +48736,7 @@
         <v>55</v>
       </c>
       <c r="P1156" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q1156" s="16"/>
       <c r="R1156" s="14" t="s">
@@ -48761,7 +48764,7 @@
         <v>2.0</v>
       </c>
       <c r="I1157" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1157" s="1">
         <v>70.0</v>
@@ -48798,7 +48801,7 @@
         <v>2.7</v>
       </c>
       <c r="I1158" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1158" s="1">
         <v>50.0</v>
@@ -48835,7 +48838,7 @@
         <v>2.5</v>
       </c>
       <c r="I1159" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1159" s="1">
         <v>50.0</v>
@@ -48946,7 +48949,7 @@
         <v>2.6</v>
       </c>
       <c r="I1162" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1162" s="1">
         <v>50.0</v>
@@ -48958,7 +48961,7 @@
         <v>55</v>
       </c>
       <c r="P1162" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q1162" s="16"/>
       <c r="R1162" s="14" t="s">
@@ -48986,7 +48989,7 @@
         <v>1.3</v>
       </c>
       <c r="I1163" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1163" s="1">
         <v>40.0</v>
@@ -48998,7 +49001,7 @@
         <v>55</v>
       </c>
       <c r="P1163" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q1163" s="16"/>
       <c r="R1163" s="14" t="s">
@@ -49026,7 +49029,7 @@
         <v>2.0</v>
       </c>
       <c r="I1164" s="15" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="M1164" s="1">
         <v>20.0</v>
@@ -49063,7 +49066,7 @@
         <v>2.2</v>
       </c>
       <c r="I1165" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1165" s="1">
         <v>40.0</v>
@@ -49075,7 +49078,7 @@
         <v>55</v>
       </c>
       <c r="P1165" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q1165" s="16"/>
       <c r="R1165" s="14" t="s">
@@ -49103,7 +49106,7 @@
         <v>2.5</v>
       </c>
       <c r="I1166" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1166" s="1">
         <v>50.0</v>
@@ -49446,7 +49449,7 @@
         <v>6.7</v>
       </c>
       <c r="I1176" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1176" s="1">
         <v>15.0</v>
@@ -49480,7 +49483,7 @@
         <v>6.7</v>
       </c>
       <c r="I1177" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1177" s="1">
         <v>10.0</v>
@@ -49514,7 +49517,7 @@
         <v>6.3</v>
       </c>
       <c r="I1178" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1178" s="1">
         <v>10.0</v>
@@ -49650,7 +49653,7 @@
         <v>6.4</v>
       </c>
       <c r="I1182" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1182" s="1">
         <v>30.0</v>
@@ -49684,7 +49687,7 @@
         <v>3.6</v>
       </c>
       <c r="I1183" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1183" s="1">
         <v>40.0</v>
@@ -49696,7 +49699,7 @@
         <v>55</v>
       </c>
       <c r="P1183" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q1183" s="16"/>
       <c r="R1183" s="14" t="s">
@@ -49733,7 +49736,7 @@
         <v>55</v>
       </c>
       <c r="P1184" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q1184" s="16"/>
       <c r="R1184" s="14" t="s">
@@ -49758,7 +49761,7 @@
         <v>3.0</v>
       </c>
       <c r="I1185" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1185" s="1">
         <v>40.0</v>
@@ -49770,7 +49773,7 @@
         <v>55</v>
       </c>
       <c r="P1185" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q1185" s="16"/>
       <c r="R1185" s="14" t="s">
@@ -49795,7 +49798,7 @@
         <v>2.6</v>
       </c>
       <c r="I1186" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1186" s="1">
         <v>40.0</v>
@@ -49829,7 +49832,7 @@
         <v>3.0</v>
       </c>
       <c r="I1187" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1187" s="1">
         <v>40.0</v>
@@ -49841,7 +49844,7 @@
         <v>55</v>
       </c>
       <c r="P1187" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q1187" s="16"/>
       <c r="R1187" s="14" t="s">
@@ -49866,7 +49869,7 @@
         <v>3.2</v>
       </c>
       <c r="I1188" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M1188" s="1">
         <v>40.0</v>
@@ -49878,7 +49881,7 @@
         <v>55</v>
       </c>
       <c r="P1188" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q1188" s="16"/>
       <c r="R1188" s="14" t="s">
@@ -49903,7 +49906,7 @@
         <v>3.0</v>
       </c>
       <c r="I1189" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M1189" s="1">
         <v>30.0</v>
